--- a/lp/koji-kanryo-hokokusho-template.xlsx
+++ b/lp/koji-kanryo-hokokusho-template.xlsx
@@ -1734,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B21"/>
+  <dimension ref="B2:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1857,6 +1857,23 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>どんな体裁で届くのかは、納品サンプル（全3ページ）で先に見られます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>https://rental-space.net/lp/sekou-report-sample.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2"/>
